--- a/INSTANCES/OAMRP-Data/8-aircraft/Cases_11-20.xlsx
+++ b/INSTANCES/OAMRP-Data/8-aircraft/Cases_11-20.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Sheet5" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Sheet6" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Sheet7" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Sheet8" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Sheet9" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Sheet10" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Sheet11" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet12" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet13" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Sheet14" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Sheet15" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Sheet16" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Sheet17" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Sheet18" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Sheet19" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Sheet20" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -297,7 +297,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W22"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -901,7 +901,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1007,8 +1007,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1019,7 +1019,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1125,8 +1125,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1137,7 +1137,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1243,8 +1243,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1255,7 +1255,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1361,8 +1361,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1373,7 +1373,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1479,8 +1479,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1491,7 +1491,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1597,8 +1597,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1609,7 +1609,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1715,8 +1715,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1727,7 +1727,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1833,8 +1833,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1845,7 +1845,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1951,8 +1951,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>